--- a/output/roomself_excel/11538.xlsx
+++ b/output/roomself_excel/11538.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>180575</v>
+        <v>74440</v>
       </c>
       <c r="D2" t="n">
-        <v>4592</v>
+        <v>2236</v>
       </c>
       <c r="E2" t="n">
-        <v>966</v>
+        <v>364</v>
       </c>
       <c r="F2" t="n">
-        <v>597</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11433</v>
+        <v>115818</v>
       </c>
       <c r="D3" t="n">
-        <v>884</v>
+        <v>2740</v>
       </c>
       <c r="E3" t="n">
-        <v>456</v>
+        <v>410</v>
       </c>
       <c r="F3" t="n">
-        <v>70</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9261</v>
+        <v>76480</v>
       </c>
       <c r="D4" t="n">
-        <v>852</v>
+        <v>2236</v>
       </c>
       <c r="E4" t="n">
-        <v>180</v>
+        <v>341</v>
       </c>
       <c r="F4" t="n">
-        <v>96</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>76480</v>
+        <v>11433</v>
       </c>
       <c r="D5" t="n">
-        <v>2236</v>
+        <v>884</v>
       </c>
       <c r="E5" t="n">
-        <v>341</v>
+        <v>110</v>
       </c>
       <c r="F5" t="n">
-        <v>260</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25575</v>
+        <v>64757</v>
       </c>
       <c r="D7" t="n">
-        <v>1280</v>
+        <v>2244</v>
       </c>
       <c r="E7" t="n">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="F7" t="n">
-        <v>176</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>74440</v>
+        <v>9261</v>
       </c>
       <c r="D8" t="n">
-        <v>2236</v>
+        <v>852</v>
       </c>
       <c r="E8" t="n">
-        <v>471</v>
+        <v>180</v>
       </c>
       <c r="F8" t="n">
-        <v>239</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>25575</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1280</v>
+      </c>
+      <c r="E9" t="n">
+        <v>186</v>
+      </c>
+      <c r="F9" t="n">
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/11538.xlsx
+++ b/output/roomself_excel/11538.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2236</v>
       </c>
-      <c r="E2" t="n">
-        <v>364</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>239</v>
+      </c>
+      <c r="G2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>290</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>2740</v>
       </c>
-      <c r="E3" t="n">
-        <v>410</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>333</v>
+        <v>368</v>
+      </c>
+      <c r="G3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>377</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>2236</v>
       </c>
-      <c r="E4" t="n">
-        <v>341</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>260</v>
+        <v>320</v>
+      </c>
+      <c r="G4" t="n">
+        <v>21</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>239</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +609,27 @@
       <c r="D5" t="n">
         <v>884</v>
       </c>
-      <c r="E5" t="n">
-        <v>110</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>70</v>
+        <v>89</v>
+      </c>
+      <c r="G5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>28</v>
+      </c>
+      <c r="J5" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +647,20 @@
       <c r="D6" t="n">
         <v>1400</v>
       </c>
-      <c r="E6" t="n">
-        <v>195</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>89</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +677,27 @@
       <c r="D7" t="n">
         <v>2244</v>
       </c>
-      <c r="E7" t="n">
-        <v>203</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>99</v>
+        <v>183</v>
+      </c>
+      <c r="G7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>57</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +715,20 @@
       <c r="D8" t="n">
         <v>852</v>
       </c>
-      <c r="E8" t="n">
-        <v>180</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>96</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="G8" t="n">
+        <v>21</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +745,27 @@
       <c r="D9" t="n">
         <v>1280</v>
       </c>
-      <c r="E9" t="n">
-        <v>186</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>176</v>
+        <v>155</v>
+      </c>
+      <c r="G9" t="n">
+        <v>21</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>165</v>
+      </c>
+      <c r="J9" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
